--- a/profiles/software/profile-crate/ro-crate-metadata.xlsx
+++ b/profiles/software/profile-crate/ro-crate-metadata.xlsx
@@ -767,25 +767,25 @@
     <t>ro-crate-metadata.json</t>
   </si>
   <si>
+    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/1149</t>
+  </si>
+  <si>
+    <t>DigitalFormat</t>
+  </si>
+  <si>
+    <t>Markdown</t>
+  </si>
+  <si>
+    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/471</t>
+  </si>
+  <si>
+    <t>Hypertext Markup Language</t>
+  </si>
+  <si>
     <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/817</t>
   </si>
   <si>
-    <t>DigitalFormat</t>
-  </si>
-  <si>
     <t>JSON Data Interchange Format</t>
-  </si>
-  <si>
-    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/471</t>
-  </si>
-  <si>
-    <t>Hypertext Markup Language</t>
-  </si>
-  <si>
-    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/1149</t>
-  </si>
-  <si>
-    <t>Markdown</t>
   </si>
 </sst>
 </file>

--- a/profiles/software/profile-crate/ro-crate-metadata.xlsx
+++ b/profiles/software/profile-crate/ro-crate-metadata.xlsx
@@ -417,7 +417,7 @@
     <t>"#RO-Crate_Metadata_Descriptor"</t>
   </si>
   <si>
-    <t>["#Root_Data_Entity", "#propertyValue_RO-Crate_Metadata_Descriptor.id"]</t>
+    <t>"#propertyValue_RO-Crate_Metadata_Descriptor.id"</t>
   </si>
   <si>
     <t>#RO-Crate_Metadata_Descriptor.about</t>
